--- a/runs/yolo11n_fcl26.04.2026-2/training_metrics.xlsx
+++ b/runs/yolo11n_fcl26.04.2026-2/training_metrics.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,8 +44,12 @@
       <color rgb="00555555"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +59,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF3FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,13 +93,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -456,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:Y55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -613,6 +628,4158 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>1.5093</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.9288</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>1.0745</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0.9241</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>0.9465</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>0.5206</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>0.5326</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>0.7751</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>0.3734</v>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>0.8595</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>0.6803</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>0.7534999999999999</v>
+      </c>
+      <c r="S2" s="4" t="n">
+        <v>0.4967</v>
+      </c>
+      <c r="T2" s="4" t="n">
+        <v>0.7081</v>
+      </c>
+      <c r="U2" s="4" t="n">
+        <v>0.7983</v>
+      </c>
+      <c r="V2" s="4" t="n">
+        <v>0.0692</v>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>0.0562</v>
+      </c>
+      <c r="X2" s="4" t="n">
+        <v>0.2356</v>
+      </c>
+      <c r="Y2" s="4" t="n">
+        <v>0.0833</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>0.00997</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>1.8245</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>1.5902</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>1.0921</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>1.0179</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.8727</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>0.9445</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>0.6899</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>0.5535</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>0.6143</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>0.5635</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="N3" s="5" t="n">
+        <v>0.7929</v>
+      </c>
+      <c r="O3" s="5" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="P3" s="5" t="n">
+        <v>0.823</v>
+      </c>
+      <c r="Q3" s="5" t="n">
+        <v>0.7504</v>
+      </c>
+      <c r="R3" s="5" t="n">
+        <v>0.7823</v>
+      </c>
+      <c r="S3" s="5" t="n">
+        <v>0.5037</v>
+      </c>
+      <c r="T3" s="5" t="n">
+        <v>0.7422</v>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="V3" s="5" t="n">
+        <v>0.1153</v>
+      </c>
+      <c r="W3" s="5" t="n">
+        <v>0.0946</v>
+      </c>
+      <c r="X3" s="5" t="n">
+        <v>0.5046</v>
+      </c>
+      <c r="Y3" s="5" t="n">
+        <v>0.0833</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>0.009939999999999999</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>1.4073</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>1.644</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0.7307</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>1.1319</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0.9147999999999999</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0.9457</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>0.5319</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>0.5269</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>0.5094</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>0.7804</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>0.7473</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>0.8106</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>0.7064</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>0.4474</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>0.7418</v>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>0.7017</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>0.0326</v>
+      </c>
+      <c r="X4" s="4" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="Y4" s="4" t="n">
+        <v>0.0833</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0.00991</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1.2797</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1.5544</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.6961000000000001</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.9734</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.9268</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0.9357</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0.6151</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0.6311</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>0.8211000000000001</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>0.4106</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>0.8846000000000001</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>0.7282999999999999</v>
+      </c>
+      <c r="R5" s="5" t="n">
+        <v>0.7917999999999999</v>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>0.7007</v>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>0.8255</v>
+      </c>
+      <c r="V5" s="5" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="W5" s="5" t="n">
+        <v>0.2095</v>
+      </c>
+      <c r="X5" s="5" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="Y5" s="5" t="n">
+        <v>0.2917</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>0.00988</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1.3322</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>1.4853</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0.6758</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0.8839</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0.9187</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0.9233</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0.6897</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>0.6556999999999999</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0.6722</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0.6812</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0.4189</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0.8459</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>0.4451</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>0.8818</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>0.7977</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>0.8509</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>0.5532</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>0.7631</v>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>0.8776</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="W6" s="4" t="n">
+        <v>0.2583</v>
+      </c>
+      <c r="X6" s="4" t="n">
+        <v>0.4242</v>
+      </c>
+      <c r="Y6" s="4" t="n">
+        <v>0.2917</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0.009849999999999999</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1.2546</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.4352</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.6618000000000001</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.8608</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.9004</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0.9108000000000001</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>0.6967</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>0.4367</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>0.8613</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>0.4633</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>0.9038</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>0.7799</v>
+      </c>
+      <c r="R7" s="5" t="n">
+        <v>0.8393</v>
+      </c>
+      <c r="S7" s="5" t="n">
+        <v>0.5453</v>
+      </c>
+      <c r="T7" s="5" t="n">
+        <v>0.7871</v>
+      </c>
+      <c r="U7" s="5" t="n">
+        <v>0.8449</v>
+      </c>
+      <c r="V7" s="5" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="W7" s="5" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="X7" s="5" t="n">
+        <v>0.7269</v>
+      </c>
+      <c r="Y7" s="5" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>0.009820000000000001</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>1.4271</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0.8315</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0.8005</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0.9035</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0.8698</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>0.6633</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0.7526</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0.4468</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>0.4704</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>0.8641</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>0.8531</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>0.8542999999999999</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>0.5767</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>0.7452</v>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>0.8922</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>0.4136</v>
+      </c>
+      <c r="W8" s="4" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="X8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="4" t="n">
+        <v>0.2446</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0.00979</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.0283</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.3999</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.5157</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.8101</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.8109</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>0.8995</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0.7523</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>0.7086</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0.7298</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>0.7421</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>0.4733</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>0.8875</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>0.4791</v>
+      </c>
+      <c r="P9" s="5" t="n">
+        <v>0.9036999999999999</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="R9" s="5" t="n">
+        <v>0.8621</v>
+      </c>
+      <c r="S9" s="5" t="n">
+        <v>0.5827</v>
+      </c>
+      <c r="T9" s="5" t="n">
+        <v>0.7758</v>
+      </c>
+      <c r="U9" s="5" t="n">
+        <v>0.8832</v>
+      </c>
+      <c r="V9" s="5" t="n">
+        <v>0.4767</v>
+      </c>
+      <c r="W9" s="5" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="X9" s="5" t="n">
+        <v>0.5773</v>
+      </c>
+      <c r="Y9" s="5" t="n">
+        <v>0.4167</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>0.00976</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1.7881</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1.3822</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0.7212</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0.7952</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1.2832</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>0.8995</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0.7516</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>0.6866</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0.7177</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>0.7375</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>0.8928</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>0.4883</v>
+      </c>
+      <c r="P10" s="4" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>0.8315</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>0.8845</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>0.5931</v>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>0.7965</v>
+      </c>
+      <c r="U10" s="4" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>0.4353</v>
+      </c>
+      <c r="W10" s="4" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="X10" s="4" t="n">
+        <v>0.5504</v>
+      </c>
+      <c r="Y10" s="4" t="n">
+        <v>0.3333</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0.009730000000000001</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1.573</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1.3719</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.6899</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0.7756999999999999</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.8148</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0.8958</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>0.7599</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>0.7218</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0.7403</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>0.7321</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>0.4685</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>0.8972</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>0.4916</v>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>0.8818</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>0.8709</v>
+      </c>
+      <c r="R11" s="5" t="n">
+        <v>0.8724</v>
+      </c>
+      <c r="S11" s="5" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="T11" s="5" t="n">
+        <v>0.7645</v>
+      </c>
+      <c r="U11" s="5" t="n">
+        <v>0.9193</v>
+      </c>
+      <c r="V11" s="5" t="n">
+        <v>0.4266</v>
+      </c>
+      <c r="W11" s="5" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="X11" s="5" t="n">
+        <v>0.6334</v>
+      </c>
+      <c r="Y11" s="5" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>1.1114</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>1.3607</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0.5583</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.7728</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0.8531</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0.8931</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0.7161</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>0.7125</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>0.7321</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0.4643</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0.8958</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>0.4922</v>
+      </c>
+      <c r="P12" s="4" t="n">
+        <v>0.8643999999999999</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>0.8841</v>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>0.8777</v>
+      </c>
+      <c r="S12" s="4" t="n">
+        <v>0.5875</v>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>0.7582</v>
+      </c>
+      <c r="U12" s="4" t="n">
+        <v>0.9298</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>0.4227</v>
+      </c>
+      <c r="W12" s="4" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="X12" s="4" t="n">
+        <v>0.5256</v>
+      </c>
+      <c r="Y12" s="4" t="n">
+        <v>0.3237</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0.00967</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.2108</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.3539</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.6165</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.7593</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.8623</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>0.8925999999999999</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>0.7939000000000001</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>0.7471</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0.7698</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>0.7745</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>0.5062</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>0.9023</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>0.4986</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>0.8942</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>0.8653999999999999</v>
+      </c>
+      <c r="R13" s="5" t="n">
+        <v>0.8957000000000001</v>
+      </c>
+      <c r="S13" s="5" t="n">
+        <v>0.6029</v>
+      </c>
+      <c r="T13" s="5" t="n">
+        <v>0.8012</v>
+      </c>
+      <c r="U13" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="V13" s="5" t="n">
+        <v>0.5255</v>
+      </c>
+      <c r="W13" s="5" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="X13" s="5" t="n">
+        <v>0.6863</v>
+      </c>
+      <c r="Y13" s="5" t="n">
+        <v>0.456</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>0.009639999999999999</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>1.117</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>1.3381</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0.5675</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.7503</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0.8946</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0.8903</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0.7764</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>0.7599</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0.7681</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>0.7801</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0.5011</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0.9092</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>0.5028</v>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v>0.8685</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>0.8923</v>
+      </c>
+      <c r="R14" s="4" t="n">
+        <v>0.8905</v>
+      </c>
+      <c r="S14" s="4" t="n">
+        <v>0.5994</v>
+      </c>
+      <c r="T14" s="4" t="n">
+        <v>0.7756999999999999</v>
+      </c>
+      <c r="U14" s="4" t="n">
+        <v>0.9291</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>0.5407</v>
+      </c>
+      <c r="W14" s="4" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="X14" s="4" t="n">
+        <v>0.6851</v>
+      </c>
+      <c r="Y14" s="4" t="n">
+        <v>0.4583</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0.00961</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9844000000000001</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.3449</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.4983</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.7469</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.8464</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>0.8908</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>0.7542</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>0.7392</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0.7466</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>0.7549</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>0.4785</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>0.9132</v>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>0.9015</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>0.8732</v>
+      </c>
+      <c r="R15" s="5" t="n">
+        <v>0.9004</v>
+      </c>
+      <c r="S15" s="5" t="n">
+        <v>0.603</v>
+      </c>
+      <c r="T15" s="5" t="n">
+        <v>0.7825</v>
+      </c>
+      <c r="U15" s="5" t="n">
+        <v>0.9277</v>
+      </c>
+      <c r="V15" s="5" t="n">
+        <v>0.4511</v>
+      </c>
+      <c r="W15" s="5" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="X15" s="5" t="n">
+        <v>0.5786</v>
+      </c>
+      <c r="Y15" s="5" t="n">
+        <v>0.4167</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>0.00958</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>1.1021</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>1.3405</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0.5155999999999999</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0.7429</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0.8397</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>0.8914</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0.7684</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>0.7286</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>0.7514</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>0.4783</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>0.9121</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>0.5044999999999999</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>0.9126</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>0.8541</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>0.8895</v>
+      </c>
+      <c r="S16" s="4" t="n">
+        <v>0.6006</v>
+      </c>
+      <c r="T16" s="4" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="U16" s="4" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>0.4525</v>
+      </c>
+      <c r="W16" s="4" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="X16" s="4" t="n">
+        <v>0.5918</v>
+      </c>
+      <c r="Y16" s="4" t="n">
+        <v>0.4167</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0.009549999999999999</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1.3369</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1.3305</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.5962</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.8607</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.8894</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0.7704</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>0.7469</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0.7585</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>0.7621</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>0.4898</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>0.9119</v>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>0.8834</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>0.8893</v>
+      </c>
+      <c r="R17" s="5" t="n">
+        <v>0.8961</v>
+      </c>
+      <c r="S17" s="5" t="n">
+        <v>0.6058</v>
+      </c>
+      <c r="T17" s="5" t="n">
+        <v>0.7784</v>
+      </c>
+      <c r="U17" s="5" t="n">
+        <v>0.9346</v>
+      </c>
+      <c r="V17" s="5" t="n">
+        <v>0.4783</v>
+      </c>
+      <c r="W17" s="5" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="X17" s="5" t="n">
+        <v>0.6495</v>
+      </c>
+      <c r="Y17" s="5" t="n">
+        <v>0.4167</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>0.009520000000000001</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>1.0966</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>1.3291</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0.6021</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0.7361</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0.8298</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0.8891</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0.7713</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>0.7335</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>0.7519</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>0.7604</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>0.4939</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>0.9121</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>0.5093</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>0.9028</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>0.8668</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>0.8914</v>
+      </c>
+      <c r="S18" s="4" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="T18" s="4" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="U18" s="4" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>0.4777</v>
+      </c>
+      <c r="W18" s="4" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="X18" s="4" t="n">
+        <v>0.6152</v>
+      </c>
+      <c r="Y18" s="4" t="n">
+        <v>0.4167</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0.00949</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1.5625</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0.7582</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0.7338</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0.8895999999999999</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>0.7857</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>0.7343</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0.7591</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>0.4857</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>0.9163</v>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>0.5088</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <v>0.8679</v>
+      </c>
+      <c r="R19" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="S19" s="5" t="n">
+        <v>0.5988</v>
+      </c>
+      <c r="T19" s="5" t="n">
+        <v>0.7967</v>
+      </c>
+      <c r="U19" s="5" t="n">
+        <v>0.9184</v>
+      </c>
+      <c r="V19" s="5" t="n">
+        <v>0.4766</v>
+      </c>
+      <c r="W19" s="5" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="X19" s="5" t="n">
+        <v>0.6574</v>
+      </c>
+      <c r="Y19" s="5" t="n">
+        <v>0.4167</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>0.00946</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>0.9416</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>1.3244</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>0.4745</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0.7315</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0.8131</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0.7657</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>0.7791</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>0.7723</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>0.7746</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>0.4964</v>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>0.9154</v>
+      </c>
+      <c r="O20" s="4" t="n">
+        <v>0.5091</v>
+      </c>
+      <c r="P20" s="4" t="n">
+        <v>0.8675</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>0.9011</v>
+      </c>
+      <c r="R20" s="4" t="n">
+        <v>0.8943</v>
+      </c>
+      <c r="S20" s="4" t="n">
+        <v>0.6012</v>
+      </c>
+      <c r="T20" s="4" t="n">
+        <v>0.7683</v>
+      </c>
+      <c r="U20" s="4" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="V20" s="4" t="n">
+        <v>0.5141</v>
+      </c>
+      <c r="W20" s="4" t="n">
+        <v>0.3789</v>
+      </c>
+      <c r="X20" s="4" t="n">
+        <v>0.6612</v>
+      </c>
+      <c r="Y20" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0.009429999999999999</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0.9474</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1.3238</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0.5004999999999999</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0.7299</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.8238</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>0.8887</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>0.7369</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>0.8121</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>0.7726</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>0.5023</v>
+      </c>
+      <c r="N21" s="5" t="n">
+        <v>0.9159</v>
+      </c>
+      <c r="O21" s="5" t="n">
+        <v>0.5086000000000001</v>
+      </c>
+      <c r="P21" s="5" t="n">
+        <v>0.8103</v>
+      </c>
+      <c r="Q21" s="5" t="n">
+        <v>0.9204</v>
+      </c>
+      <c r="R21" s="5" t="n">
+        <v>0.8905</v>
+      </c>
+      <c r="S21" s="5" t="n">
+        <v>0.5988</v>
+      </c>
+      <c r="T21" s="5" t="n">
+        <v>0.7383</v>
+      </c>
+      <c r="U21" s="5" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="V21" s="5" t="n">
+        <v>0.5425</v>
+      </c>
+      <c r="W21" s="5" t="n">
+        <v>0.3995</v>
+      </c>
+      <c r="X21" s="5" t="n">
+        <v>0.6619</v>
+      </c>
+      <c r="Y21" s="5" t="n">
+        <v>0.5715</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>1.4602</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>1.3227</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>0.8457</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0.7276</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0.9133</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>0.8887</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>0.8013</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>0.7759</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>0.7837</v>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>0.5038</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>0.9173</v>
+      </c>
+      <c r="O22" s="4" t="n">
+        <v>0.5101</v>
+      </c>
+      <c r="P22" s="4" t="n">
+        <v>0.9076</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>0.8733</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>0.8915999999999999</v>
+      </c>
+      <c r="S22" s="4" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="T22" s="4" t="n">
+        <v>0.7874</v>
+      </c>
+      <c r="U22" s="4" t="n">
+        <v>0.9244</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>0.5423</v>
+      </c>
+      <c r="W22" s="4" t="n">
+        <v>0.3993</v>
+      </c>
+      <c r="X22" s="4" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="Y22" s="4" t="n">
+        <v>0.4583</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0.00937</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>1.0739</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1.3211</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.6012999999999999</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.7269</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.8815</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>0.7833</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>0.7638</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0.7734</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>0.7884</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>0.5096000000000001</v>
+      </c>
+      <c r="N23" s="5" t="n">
+        <v>0.9154</v>
+      </c>
+      <c r="O23" s="5" t="n">
+        <v>0.5106000000000001</v>
+      </c>
+      <c r="P23" s="5" t="n">
+        <v>0.8816000000000001</v>
+      </c>
+      <c r="Q23" s="5" t="n">
+        <v>0.8924</v>
+      </c>
+      <c r="R23" s="5" t="n">
+        <v>0.8912</v>
+      </c>
+      <c r="S23" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T23" s="5" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="U23" s="5" t="n">
+        <v>0.9277</v>
+      </c>
+      <c r="V23" s="5" t="n">
+        <v>0.5585</v>
+      </c>
+      <c r="W23" s="5" t="n">
+        <v>0.4182</v>
+      </c>
+      <c r="X23" s="5" t="n">
+        <v>0.6932</v>
+      </c>
+      <c r="Y23" s="5" t="n">
+        <v>0.4713</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>0.009339999999999999</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>0.8279</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0.7267</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>0.8444</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>0.7677</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>0.7762</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>0.7911</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>0.5131</v>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>0.9164</v>
+      </c>
+      <c r="O24" s="4" t="n">
+        <v>0.5111</v>
+      </c>
+      <c r="P24" s="4" t="n">
+        <v>0.8625</v>
+      </c>
+      <c r="Q24" s="4" t="n">
+        <v>0.9046999999999999</v>
+      </c>
+      <c r="R24" s="4" t="n">
+        <v>0.8914</v>
+      </c>
+      <c r="S24" s="4" t="n">
+        <v>0.6006</v>
+      </c>
+      <c r="T24" s="4" t="n">
+        <v>0.7669</v>
+      </c>
+      <c r="U24" s="4" t="n">
+        <v>0.9332</v>
+      </c>
+      <c r="V24" s="4" t="n">
+        <v>0.5654</v>
+      </c>
+      <c r="W24" s="4" t="n">
+        <v>0.4277</v>
+      </c>
+      <c r="X24" s="4" t="n">
+        <v>0.6738</v>
+      </c>
+      <c r="Y24" s="4" t="n">
+        <v>0.517</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0.009310000000000001</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>1.2262</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>1.3182</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0.5551</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0.7257</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.8885999999999999</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0.8889</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>0.8087</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>0.7647</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>0.7861</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>0.7921</v>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>0.5088</v>
+      </c>
+      <c r="N25" s="5" t="n">
+        <v>0.9164</v>
+      </c>
+      <c r="O25" s="5" t="n">
+        <v>0.5117</v>
+      </c>
+      <c r="P25" s="5" t="n">
+        <v>0.8973</v>
+      </c>
+      <c r="Q25" s="5" t="n">
+        <v>0.8791</v>
+      </c>
+      <c r="R25" s="5" t="n">
+        <v>0.8907</v>
+      </c>
+      <c r="S25" s="5" t="n">
+        <v>0.5994</v>
+      </c>
+      <c r="T25" s="5" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="U25" s="5" t="n">
+        <v>0.9256</v>
+      </c>
+      <c r="V25" s="5" t="n">
+        <v>0.5692</v>
+      </c>
+      <c r="W25" s="5" t="n">
+        <v>0.4153</v>
+      </c>
+      <c r="X25" s="5" t="n">
+        <v>0.7457</v>
+      </c>
+      <c r="Y25" s="5" t="n">
+        <v>0.4893</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>0.00928</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>1.1006</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>1.3171</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>0.6233</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>0.7254</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>0.8129</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>0.7919</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>0.7546</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>0.7728</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>0.7869</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>0.5053</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>0.9167</v>
+      </c>
+      <c r="O26" s="4" t="n">
+        <v>0.5118</v>
+      </c>
+      <c r="P26" s="4" t="n">
+        <v>0.8962</v>
+      </c>
+      <c r="Q26" s="4" t="n">
+        <v>0.8801</v>
+      </c>
+      <c r="R26" s="4" t="n">
+        <v>0.8907</v>
+      </c>
+      <c r="S26" s="4" t="n">
+        <v>0.6007</v>
+      </c>
+      <c r="T26" s="4" t="n">
+        <v>0.7843</v>
+      </c>
+      <c r="U26" s="4" t="n">
+        <v>0.9253</v>
+      </c>
+      <c r="V26" s="4" t="n">
+        <v>0.5532</v>
+      </c>
+      <c r="W26" s="4" t="n">
+        <v>0.4033</v>
+      </c>
+      <c r="X26" s="4" t="n">
+        <v>0.6951000000000001</v>
+      </c>
+      <c r="Y26" s="4" t="n">
+        <v>0.4583</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0.00925</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>1.1588</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>1.3166</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0.5982</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0.7245</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>1.0414</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>0.8891</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>0.7373</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>0.7882</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>0.5068</v>
+      </c>
+      <c r="N27" s="5" t="n">
+        <v>0.9176</v>
+      </c>
+      <c r="O27" s="5" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="P27" s="5" t="n">
+        <v>0.8292</v>
+      </c>
+      <c r="Q27" s="5" t="n">
+        <v>0.9173</v>
+      </c>
+      <c r="R27" s="5" t="n">
+        <v>0.8908</v>
+      </c>
+      <c r="S27" s="5" t="n">
+        <v>0.6014</v>
+      </c>
+      <c r="T27" s="5" t="n">
+        <v>0.7413999999999999</v>
+      </c>
+      <c r="U27" s="5" t="n">
+        <v>0.9432</v>
+      </c>
+      <c r="V27" s="5" t="n">
+        <v>0.5563</v>
+      </c>
+      <c r="W27" s="5" t="n">
+        <v>0.4064</v>
+      </c>
+      <c r="X27" s="5" t="n">
+        <v>0.6414</v>
+      </c>
+      <c r="Y27" s="5" t="n">
+        <v>0.5965</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>0.009220000000000001</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>1.2881</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>1.3168</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>0.5962</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>0.7247</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>0.8237</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>0.8892</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>0.8135</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>0.7766999999999999</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>0.7849</v>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>0.5038</v>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>0.9179</v>
+      </c>
+      <c r="O28" s="4" t="n">
+        <v>0.5129</v>
+      </c>
+      <c r="P28" s="4" t="n">
+        <v>0.8415</v>
+      </c>
+      <c r="Q28" s="4" t="n">
+        <v>0.9154</v>
+      </c>
+      <c r="R28" s="4" t="n">
+        <v>0.8901</v>
+      </c>
+      <c r="S28" s="4" t="n">
+        <v>0.6018</v>
+      </c>
+      <c r="T28" s="4" t="n">
+        <v>0.7504999999999999</v>
+      </c>
+      <c r="U28" s="4" t="n">
+        <v>0.9402</v>
+      </c>
+      <c r="V28" s="4" t="n">
+        <v>0.5467</v>
+      </c>
+      <c r="W28" s="4" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="X28" s="4" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="Y28" s="4" t="n">
+        <v>0.5849</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0.00919</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>0.9681999999999999</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>1.316</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0.5864</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0.7248</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.8262</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>0.8895999999999999</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>0.7575</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>0.8061</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>0.5034</v>
+      </c>
+      <c r="N29" s="5" t="n">
+        <v>0.9177999999999999</v>
+      </c>
+      <c r="O29" s="5" t="n">
+        <v>0.5135999999999999</v>
+      </c>
+      <c r="P29" s="5" t="n">
+        <v>0.8532</v>
+      </c>
+      <c r="Q29" s="5" t="n">
+        <v>0.9117</v>
+      </c>
+      <c r="R29" s="5" t="n">
+        <v>0.8897</v>
+      </c>
+      <c r="S29" s="5" t="n">
+        <v>0.5992</v>
+      </c>
+      <c r="T29" s="5" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="U29" s="5" t="n">
+        <v>0.9367</v>
+      </c>
+      <c r="V29" s="5" t="n">
+        <v>0.5506</v>
+      </c>
+      <c r="W29" s="5" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="X29" s="5" t="n">
+        <v>0.6613</v>
+      </c>
+      <c r="Y29" s="5" t="n">
+        <v>0.5699</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>0.00916</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>0.9553</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>1.3173</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>0.4669</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>0.7233000000000001</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>0.8055</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>0.8898</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>0.7609</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>0.8073</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>0.7834</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>0.7849</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>0.5034</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>0.9177</v>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>0.5131</v>
+      </c>
+      <c r="P30" s="4" t="n">
+        <v>0.8566</v>
+      </c>
+      <c r="Q30" s="4" t="n">
+        <v>0.9087</v>
+      </c>
+      <c r="R30" s="4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="S30" s="4" t="n">
+        <v>0.5992</v>
+      </c>
+      <c r="T30" s="4" t="n">
+        <v>0.7615</v>
+      </c>
+      <c r="U30" s="4" t="n">
+        <v>0.9353</v>
+      </c>
+      <c r="V30" s="4" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="W30" s="4" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="X30" s="4" t="n">
+        <v>0.6645</v>
+      </c>
+      <c r="Y30" s="4" t="n">
+        <v>0.5779</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0.009129999999999999</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>0.8893</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>1.3166</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0.4269</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.8255</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>0.8897</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>0.7579</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>0.8074</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0.7819</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>0.7826</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>0.5006</v>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>0.9175</v>
+      </c>
+      <c r="O31" s="5" t="n">
+        <v>0.5128</v>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>0.8519</v>
+      </c>
+      <c r="Q31" s="5" t="n">
+        <v>0.9101</v>
+      </c>
+      <c r="R31" s="5" t="n">
+        <v>0.8905999999999999</v>
+      </c>
+      <c r="S31" s="5" t="n">
+        <v>0.5992</v>
+      </c>
+      <c r="T31" s="5" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="U31" s="5" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="V31" s="5" t="n">
+        <v>0.5399</v>
+      </c>
+      <c r="W31" s="5" t="n">
+        <v>0.3897</v>
+      </c>
+      <c r="X31" s="5" t="n">
+        <v>0.6637999999999999</v>
+      </c>
+      <c r="Y31" s="5" t="n">
+        <v>0.5760999999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>0.9534</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>1.3164</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>0.4658</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>0.7221</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>0.8373</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>0.8895999999999999</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>0.7543</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>0.8116</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>0.7819</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>0.7823</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="O32" s="4" t="n">
+        <v>0.5131</v>
+      </c>
+      <c r="P32" s="4" t="n">
+        <v>0.8443000000000001</v>
+      </c>
+      <c r="Q32" s="4" t="n">
+        <v>0.9135</v>
+      </c>
+      <c r="R32" s="4" t="n">
+        <v>0.8913</v>
+      </c>
+      <c r="S32" s="4" t="n">
+        <v>0.5985</v>
+      </c>
+      <c r="T32" s="4" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="U32" s="4" t="n">
+        <v>0.9381</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>0.5376</v>
+      </c>
+      <c r="W32" s="4" t="n">
+        <v>0.3884</v>
+      </c>
+      <c r="X32" s="4" t="n">
+        <v>0.6657</v>
+      </c>
+      <c r="Y32" s="4" t="n">
+        <v>0.5833</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0.00907</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>0.8925</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>1.3164</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0.7217</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.8263</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>0.8898</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>0.7561</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>0.8108</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0.7825</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>0.7815</v>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>0.4998</v>
+      </c>
+      <c r="N33" s="5" t="n">
+        <v>0.9182</v>
+      </c>
+      <c r="O33" s="5" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="P33" s="5" t="n">
+        <v>0.8468</v>
+      </c>
+      <c r="Q33" s="5" t="n">
+        <v>0.9123</v>
+      </c>
+      <c r="R33" s="5" t="n">
+        <v>0.8917</v>
+      </c>
+      <c r="S33" s="5" t="n">
+        <v>0.5996</v>
+      </c>
+      <c r="T33" s="5" t="n">
+        <v>0.7557</v>
+      </c>
+      <c r="U33" s="5" t="n">
+        <v>0.9388</v>
+      </c>
+      <c r="V33" s="5" t="n">
+        <v>0.5347</v>
+      </c>
+      <c r="W33" s="5" t="n">
+        <v>0.3868</v>
+      </c>
+      <c r="X33" s="5" t="n">
+        <v>0.6657999999999999</v>
+      </c>
+      <c r="Y33" s="5" t="n">
+        <v>0.5813</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>0.009039999999999999</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>1.0306</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>1.3174</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>0.5666</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>0.7219</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>0.8722</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>0.8899</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>0.7529</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>0.7818000000000001</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>0.7817</v>
+      </c>
+      <c r="M34" s="4" t="n">
+        <v>0.4995</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>0.9189000000000001</v>
+      </c>
+      <c r="O34" s="4" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="P34" s="4" t="n">
+        <v>0.8394</v>
+      </c>
+      <c r="Q34" s="4" t="n">
+        <v>0.9164</v>
+      </c>
+      <c r="R34" s="4" t="n">
+        <v>0.8925</v>
+      </c>
+      <c r="S34" s="4" t="n">
+        <v>0.5997</v>
+      </c>
+      <c r="T34" s="4" t="n">
+        <v>0.7534999999999999</v>
+      </c>
+      <c r="U34" s="4" t="n">
+        <v>0.9416</v>
+      </c>
+      <c r="V34" s="4" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="W34" s="4" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="X34" s="4" t="n">
+        <v>0.6657</v>
+      </c>
+      <c r="Y34" s="4" t="n">
+        <v>0.581</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0.009010000000000001</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>1.2571</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>1.3168</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0.5727</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0.7209</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.8329</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0.8901</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>0.7336</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0.7766</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>0.7836</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N35" s="5" t="n">
+        <v>0.9188</v>
+      </c>
+      <c r="O35" s="5" t="n">
+        <v>0.5123</v>
+      </c>
+      <c r="P35" s="5" t="n">
+        <v>0.8137</v>
+      </c>
+      <c r="Q35" s="5" t="n">
+        <v>0.9222</v>
+      </c>
+      <c r="R35" s="5" t="n">
+        <v>0.8922</v>
+      </c>
+      <c r="S35" s="5" t="n">
+        <v>0.6007</v>
+      </c>
+      <c r="T35" s="5" t="n">
+        <v>0.7428</v>
+      </c>
+      <c r="U35" s="5" t="n">
+        <v>0.9485</v>
+      </c>
+      <c r="V35" s="5" t="n">
+        <v>0.5397999999999999</v>
+      </c>
+      <c r="W35" s="5" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="X35" s="5" t="n">
+        <v>0.6444</v>
+      </c>
+      <c r="Y35" s="5" t="n">
+        <v>0.6044</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>0.00898</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>0.8693</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>1.3162</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>0.7205</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>0.8903</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>0.7346</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>0.8250999999999999</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>0.7772</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>0.7845</v>
+      </c>
+      <c r="M36" s="4" t="n">
+        <v>0.5033</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>0.9189000000000001</v>
+      </c>
+      <c r="O36" s="4" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="P36" s="4" t="n">
+        <v>0.8162</v>
+      </c>
+      <c r="Q36" s="4" t="n">
+        <v>0.9217</v>
+      </c>
+      <c r="R36" s="4" t="n">
+        <v>0.8915</v>
+      </c>
+      <c r="S36" s="4" t="n">
+        <v>0.6011</v>
+      </c>
+      <c r="T36" s="4" t="n">
+        <v>0.7421</v>
+      </c>
+      <c r="U36" s="4" t="n">
+        <v>0.9465</v>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>0.5432</v>
+      </c>
+      <c r="W36" s="4" t="n">
+        <v>0.3962</v>
+      </c>
+      <c r="X36" s="4" t="n">
+        <v>0.6454</v>
+      </c>
+      <c r="Y36" s="4" t="n">
+        <v>0.607</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0.00895</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>1.0325</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>1.3164</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0.5029</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0.7211</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.8227</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>0.8904</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>0.8313</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>0.7791</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>0.7844</v>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>0.5023</v>
+      </c>
+      <c r="N37" s="5" t="n">
+        <v>0.9186</v>
+      </c>
+      <c r="O37" s="5" t="n">
+        <v>0.5128</v>
+      </c>
+      <c r="P37" s="5" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="Q37" s="5" t="n">
+        <v>0.9225</v>
+      </c>
+      <c r="R37" s="5" t="n">
+        <v>0.8908</v>
+      </c>
+      <c r="S37" s="5" t="n">
+        <v>0.6007</v>
+      </c>
+      <c r="T37" s="5" t="n">
+        <v>0.7391</v>
+      </c>
+      <c r="U37" s="5" t="n">
+        <v>0.9465</v>
+      </c>
+      <c r="V37" s="5" t="n">
+        <v>0.5438</v>
+      </c>
+      <c r="W37" s="5" t="n">
+        <v>0.3935</v>
+      </c>
+      <c r="X37" s="5" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="Y37" s="5" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>0.008920000000000001</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>1.1588</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>1.3159</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>0.5152</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>0.7202</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>0.8105</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>0.8903</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>0.7291</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>0.7745</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>0.7869</v>
+      </c>
+      <c r="M38" s="4" t="n">
+        <v>0.5033</v>
+      </c>
+      <c r="N38" s="4" t="n">
+        <v>0.9184</v>
+      </c>
+      <c r="O38" s="4" t="n">
+        <v>0.5123</v>
+      </c>
+      <c r="P38" s="4" t="n">
+        <v>0.8042</v>
+      </c>
+      <c r="Q38" s="4" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="R38" s="4" t="n">
+        <v>0.8898</v>
+      </c>
+      <c r="S38" s="4" t="n">
+        <v>0.6017</v>
+      </c>
+      <c r="T38" s="4" t="n">
+        <v>0.7374000000000001</v>
+      </c>
+      <c r="U38" s="4" t="n">
+        <v>0.9471000000000001</v>
+      </c>
+      <c r="V38" s="4" t="n">
+        <v>0.5524</v>
+      </c>
+      <c r="W38" s="4" t="n">
+        <v>0.3957</v>
+      </c>
+      <c r="X38" s="4" t="n">
+        <v>0.6457000000000001</v>
+      </c>
+      <c r="Y38" s="4" t="n">
+        <v>0.6078</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0.00889</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>1.2436</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>1.3156</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0.5754</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>0.7199</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.8788</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>0.8904</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>0.7346</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>0.8315</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>0.7895</v>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>0.5031</v>
+      </c>
+      <c r="N39" s="5" t="n">
+        <v>0.9183</v>
+      </c>
+      <c r="O39" s="5" t="n">
+        <v>0.5124</v>
+      </c>
+      <c r="P39" s="5" t="n">
+        <v>0.8013</v>
+      </c>
+      <c r="Q39" s="5" t="n">
+        <v>0.9245</v>
+      </c>
+      <c r="R39" s="5" t="n">
+        <v>0.8908</v>
+      </c>
+      <c r="S39" s="5" t="n">
+        <v>0.6012</v>
+      </c>
+      <c r="T39" s="5" t="n">
+        <v>0.7366</v>
+      </c>
+      <c r="U39" s="5" t="n">
+        <v>0.9451000000000001</v>
+      </c>
+      <c r="V39" s="5" t="n">
+        <v>0.5593</v>
+      </c>
+      <c r="W39" s="5" t="n">
+        <v>0.3958</v>
+      </c>
+      <c r="X39" s="5" t="n">
+        <v>0.6657999999999999</v>
+      </c>
+      <c r="Y39" s="5" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>0.00886</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>1.3056</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>1.3159</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>0.6238</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>0.7202</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>0.8062</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>0.8905</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>0.7383999999999999</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>0.8312</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>0.7821</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>0.7901</v>
+      </c>
+      <c r="M40" s="4" t="n">
+        <v>0.5033</v>
+      </c>
+      <c r="N40" s="4" t="n">
+        <v>0.9187</v>
+      </c>
+      <c r="O40" s="4" t="n">
+        <v>0.5121</v>
+      </c>
+      <c r="P40" s="4" t="n">
+        <v>0.8053</v>
+      </c>
+      <c r="Q40" s="4" t="n">
+        <v>0.9236</v>
+      </c>
+      <c r="R40" s="4" t="n">
+        <v>0.8912</v>
+      </c>
+      <c r="S40" s="4" t="n">
+        <v>0.6011</v>
+      </c>
+      <c r="T40" s="4" t="n">
+        <v>0.7366</v>
+      </c>
+      <c r="U40" s="4" t="n">
+        <v>0.9451000000000001</v>
+      </c>
+      <c r="V40" s="4" t="n">
+        <v>0.5605</v>
+      </c>
+      <c r="W40" s="4" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="X40" s="4" t="n">
+        <v>0.6731</v>
+      </c>
+      <c r="Y40" s="4" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0.008829999999999999</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>0.9539</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>1.3162</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0.4504</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0.7208</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.8147</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>0.8908</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>0.8303</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0.7848000000000001</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>0.7887999999999999</v>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="N41" s="5" t="n">
+        <v>0.9192</v>
+      </c>
+      <c r="O41" s="5" t="n">
+        <v>0.5118</v>
+      </c>
+      <c r="P41" s="5" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="Q41" s="5" t="n">
+        <v>0.9223</v>
+      </c>
+      <c r="R41" s="5" t="n">
+        <v>0.8909</v>
+      </c>
+      <c r="S41" s="5" t="n">
+        <v>0.6007</v>
+      </c>
+      <c r="T41" s="5" t="n">
+        <v>0.7419</v>
+      </c>
+      <c r="U41" s="5" t="n">
+        <v>0.9437</v>
+      </c>
+      <c r="V41" s="5" t="n">
+        <v>0.5562</v>
+      </c>
+      <c r="W41" s="5" t="n">
+        <v>0.3995</v>
+      </c>
+      <c r="X41" s="5" t="n">
+        <v>0.6742</v>
+      </c>
+      <c r="Y41" s="5" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>1.3155</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>0.4758</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>0.7205</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>0.7839</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>0.8907</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>0.7431</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>0.8302</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>0.7842</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>0.7884</v>
+      </c>
+      <c r="M42" s="4" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="N42" s="4" t="n">
+        <v>0.9192</v>
+      </c>
+      <c r="O42" s="4" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="P42" s="4" t="n">
+        <v>0.8134</v>
+      </c>
+      <c r="Q42" s="4" t="n">
+        <v>0.9226</v>
+      </c>
+      <c r="R42" s="4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="S42" s="4" t="n">
+        <v>0.6015</v>
+      </c>
+      <c r="T42" s="4" t="n">
+        <v>0.7418</v>
+      </c>
+      <c r="U42" s="4" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="V42" s="4" t="n">
+        <v>0.5561</v>
+      </c>
+      <c r="W42" s="4" t="n">
+        <v>0.4009</v>
+      </c>
+      <c r="X42" s="4" t="n">
+        <v>0.6742</v>
+      </c>
+      <c r="Y42" s="4" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0.00877</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>1.1867</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>1.3161</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0.7203000000000001</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.8574000000000001</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>0.8908</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>0.7491</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>0.8221000000000001</v>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>0.7839</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>0.7902</v>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="N43" s="5" t="n">
+        <v>0.9192</v>
+      </c>
+      <c r="O43" s="5" t="n">
+        <v>0.5123</v>
+      </c>
+      <c r="P43" s="5" t="n">
+        <v>0.8245</v>
+      </c>
+      <c r="Q43" s="5" t="n">
+        <v>0.9202</v>
+      </c>
+      <c r="R43" s="5" t="n">
+        <v>0.8902</v>
+      </c>
+      <c r="S43" s="5" t="n">
+        <v>0.6002</v>
+      </c>
+      <c r="T43" s="5" t="n">
+        <v>0.7479</v>
+      </c>
+      <c r="U43" s="5" t="n">
+        <v>0.9402</v>
+      </c>
+      <c r="V43" s="5" t="n">
+        <v>0.5612</v>
+      </c>
+      <c r="W43" s="5" t="n">
+        <v>0.4114</v>
+      </c>
+      <c r="X43" s="5" t="n">
+        <v>0.6749000000000001</v>
+      </c>
+      <c r="Y43" s="5" t="n">
+        <v>0.6059</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>0.00874</v>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>1.1851</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>1.316</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>0.5405</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>0.7195</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>0.8984</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>0.8909</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>0.7511</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>0.8133</v>
+      </c>
+      <c r="K44" s="4" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>0.7911</v>
+      </c>
+      <c r="M44" s="4" t="n">
+        <v>0.5104</v>
+      </c>
+      <c r="N44" s="4" t="n">
+        <v>0.9196</v>
+      </c>
+      <c r="O44" s="4" t="n">
+        <v>0.5131</v>
+      </c>
+      <c r="P44" s="4" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="Q44" s="4" t="n">
+        <v>0.9177999999999999</v>
+      </c>
+      <c r="R44" s="4" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="S44" s="4" t="n">
+        <v>0.6002</v>
+      </c>
+      <c r="T44" s="4" t="n">
+        <v>0.7563</v>
+      </c>
+      <c r="U44" s="4" t="n">
+        <v>0.9388</v>
+      </c>
+      <c r="V44" s="4" t="n">
+        <v>0.5628</v>
+      </c>
+      <c r="W44" s="4" t="n">
+        <v>0.4178</v>
+      </c>
+      <c r="X44" s="4" t="n">
+        <v>0.6612</v>
+      </c>
+      <c r="Y44" s="4" t="n">
+        <v>0.5833</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0.008710000000000001</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>1.4618</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>1.3155</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>0.7187</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.9540999999999999</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>0.8911</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>0.8123</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>0.7842</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>0.7897999999999999</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>0.5101</v>
+      </c>
+      <c r="N45" s="5" t="n">
+        <v>0.9193</v>
+      </c>
+      <c r="O45" s="5" t="n">
+        <v>0.5124</v>
+      </c>
+      <c r="P45" s="5" t="n">
+        <v>0.8417</v>
+      </c>
+      <c r="Q45" s="5" t="n">
+        <v>0.9157999999999999</v>
+      </c>
+      <c r="R45" s="5" t="n">
+        <v>0.8907</v>
+      </c>
+      <c r="S45" s="5" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="T45" s="5" t="n">
+        <v>0.7595</v>
+      </c>
+      <c r="U45" s="5" t="n">
+        <v>0.9378</v>
+      </c>
+      <c r="V45" s="5" t="n">
+        <v>0.5593</v>
+      </c>
+      <c r="W45" s="5" t="n">
+        <v>0.4168</v>
+      </c>
+      <c r="X45" s="5" t="n">
+        <v>0.6727</v>
+      </c>
+      <c r="Y45" s="5" t="n">
+        <v>0.5833</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>0.00868</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>1.0495</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>1.3152</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>0.5145</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>0.7187</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>0.8911</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>0.7664</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>0.8106</v>
+      </c>
+      <c r="K46" s="4" t="n">
+        <v>0.7879</v>
+      </c>
+      <c r="L46" s="4" t="n">
+        <v>0.7895</v>
+      </c>
+      <c r="M46" s="4" t="n">
+        <v>0.5096000000000001</v>
+      </c>
+      <c r="N46" s="4" t="n">
+        <v>0.9197</v>
+      </c>
+      <c r="O46" s="4" t="n">
+        <v>0.5127</v>
+      </c>
+      <c r="P46" s="4" t="n">
+        <v>0.8502999999999999</v>
+      </c>
+      <c r="Q46" s="4" t="n">
+        <v>0.9126</v>
+      </c>
+      <c r="R46" s="4" t="n">
+        <v>0.8908</v>
+      </c>
+      <c r="S46" s="4" t="n">
+        <v>0.6007</v>
+      </c>
+      <c r="T46" s="4" t="n">
+        <v>0.7643</v>
+      </c>
+      <c r="U46" s="4" t="n">
+        <v>0.9359</v>
+      </c>
+      <c r="V46" s="4" t="n">
+        <v>0.5581</v>
+      </c>
+      <c r="W46" s="4" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="X46" s="4" t="n">
+        <v>0.6847</v>
+      </c>
+      <c r="Y46" s="4" t="n">
+        <v>0.5833</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0.00865</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>1.183</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>1.3145</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>0.7187</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.7991</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>0.7695</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>0.8085</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>0.7885</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>0.7909</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>0.5099</v>
+      </c>
+      <c r="N47" s="5" t="n">
+        <v>0.9199000000000001</v>
+      </c>
+      <c r="O47" s="5" t="n">
+        <v>0.5128</v>
+      </c>
+      <c r="P47" s="5" t="n">
+        <v>0.8557</v>
+      </c>
+      <c r="Q47" s="5" t="n">
+        <v>0.9089</v>
+      </c>
+      <c r="R47" s="5" t="n">
+        <v>0.8909</v>
+      </c>
+      <c r="S47" s="5" t="n">
+        <v>0.5995</v>
+      </c>
+      <c r="T47" s="5" t="n">
+        <v>0.7673</v>
+      </c>
+      <c r="U47" s="5" t="n">
+        <v>0.9332</v>
+      </c>
+      <c r="V47" s="5" t="n">
+        <v>0.5618</v>
+      </c>
+      <c r="W47" s="5" t="n">
+        <v>0.4175</v>
+      </c>
+      <c r="X47" s="5" t="n">
+        <v>0.6857</v>
+      </c>
+      <c r="Y47" s="5" t="n">
+        <v>0.5833</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>0.008619999999999999</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>1.1523</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>1.3146</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>0.7186</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>0.8166</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>0.8913</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>0.7586000000000001</v>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>0.7945</v>
+      </c>
+      <c r="K48" s="4" t="n">
+        <v>0.7761</v>
+      </c>
+      <c r="L48" s="4" t="n">
+        <v>0.7902</v>
+      </c>
+      <c r="M48" s="4" t="n">
+        <v>0.5093</v>
+      </c>
+      <c r="N48" s="4" t="n">
+        <v>0.9198</v>
+      </c>
+      <c r="O48" s="4" t="n">
+        <v>0.5129</v>
+      </c>
+      <c r="P48" s="4" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="Q48" s="4" t="n">
+        <v>0.9092</v>
+      </c>
+      <c r="R48" s="4" t="n">
+        <v>0.8905</v>
+      </c>
+      <c r="S48" s="4" t="n">
+        <v>0.5996</v>
+      </c>
+      <c r="T48" s="4" t="n">
+        <v>0.7645</v>
+      </c>
+      <c r="U48" s="4" t="n">
+        <v>0.9326</v>
+      </c>
+      <c r="V48" s="4" t="n">
+        <v>0.5602</v>
+      </c>
+      <c r="W48" s="4" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="X48" s="4" t="n">
+        <v>0.6541</v>
+      </c>
+      <c r="Y48" s="4" t="n">
+        <v>0.5417</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0.00859</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>1.0886</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>1.3146</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0.6035</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>0.7181999999999999</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0.8912</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>0.7604</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>0.7931</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>0.7764</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M49" s="5" t="n">
+        <v>0.5096000000000001</v>
+      </c>
+      <c r="N49" s="5" t="n">
+        <v>0.9199000000000001</v>
+      </c>
+      <c r="O49" s="5" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="P49" s="5" t="n">
+        <v>0.8623</v>
+      </c>
+      <c r="Q49" s="5" t="n">
+        <v>0.9056999999999999</v>
+      </c>
+      <c r="R49" s="5" t="n">
+        <v>0.8909</v>
+      </c>
+      <c r="S49" s="5" t="n">
+        <v>0.5995</v>
+      </c>
+      <c r="T49" s="5" t="n">
+        <v>0.7687</v>
+      </c>
+      <c r="U49" s="5" t="n">
+        <v>0.9314</v>
+      </c>
+      <c r="V49" s="5" t="n">
+        <v>0.5593</v>
+      </c>
+      <c r="W49" s="5" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="X49" s="5" t="n">
+        <v>0.6502</v>
+      </c>
+      <c r="Y49" s="5" t="n">
+        <v>0.5423</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>0.00856</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>1.061</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>1.3145</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>0.7176</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>0.8538</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>0.8911</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>0.7692</v>
+      </c>
+      <c r="J50" s="4" t="n">
+        <v>0.7913</v>
+      </c>
+      <c r="K50" s="4" t="n">
+        <v>0.7801</v>
+      </c>
+      <c r="L50" s="4" t="n">
+        <v>0.7894</v>
+      </c>
+      <c r="M50" s="4" t="n">
+        <v>0.5065</v>
+      </c>
+      <c r="N50" s="4" t="n">
+        <v>0.9206</v>
+      </c>
+      <c r="O50" s="4" t="n">
+        <v>0.5135</v>
+      </c>
+      <c r="P50" s="4" t="n">
+        <v>0.8678</v>
+      </c>
+      <c r="Q50" s="4" t="n">
+        <v>0.9036999999999999</v>
+      </c>
+      <c r="R50" s="4" t="n">
+        <v>0.8911</v>
+      </c>
+      <c r="S50" s="4" t="n">
+        <v>0.5982</v>
+      </c>
+      <c r="T50" s="4" t="n">
+        <v>0.7704</v>
+      </c>
+      <c r="U50" s="4" t="n">
+        <v>0.9284</v>
+      </c>
+      <c r="V50" s="4" t="n">
+        <v>0.5565</v>
+      </c>
+      <c r="W50" s="4" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="X50" s="4" t="n">
+        <v>0.6695</v>
+      </c>
+      <c r="Y50" s="4" t="n">
+        <v>0.5417</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>0.008529999999999999</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>1.1248</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>1.3147</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0.5207000000000001</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0.7175</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.8093</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>0.8913</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>0.7734</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>0.7901</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>0.7817</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>0.7934</v>
+      </c>
+      <c r="M51" s="5" t="n">
+        <v>0.5096000000000001</v>
+      </c>
+      <c r="N51" s="5" t="n">
+        <v>0.9197</v>
+      </c>
+      <c r="O51" s="5" t="n">
+        <v>0.5133</v>
+      </c>
+      <c r="P51" s="5" t="n">
+        <v>0.8729</v>
+      </c>
+      <c r="Q51" s="5" t="n">
+        <v>0.8998</v>
+      </c>
+      <c r="R51" s="5" t="n">
+        <v>0.8913</v>
+      </c>
+      <c r="S51" s="5" t="n">
+        <v>0.5986</v>
+      </c>
+      <c r="T51" s="5" t="n">
+        <v>0.7744</v>
+      </c>
+      <c r="U51" s="5" t="n">
+        <v>0.9287</v>
+      </c>
+      <c r="V51" s="5" t="n">
+        <v>0.5693</v>
+      </c>
+      <c r="W51" s="5" t="n">
+        <v>0.4169</v>
+      </c>
+      <c r="X51" s="5" t="n">
+        <v>0.6729000000000001</v>
+      </c>
+      <c r="Y51" s="5" t="n">
+        <v>0.5417</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>1.2553</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>1.3149</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>0.5554</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>0.7716</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>0.8917</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>0.7785</v>
+      </c>
+      <c r="J52" s="4" t="n">
+        <v>0.7902</v>
+      </c>
+      <c r="K52" s="4" t="n">
+        <v>0.7843</v>
+      </c>
+      <c r="L52" s="4" t="n">
+        <v>0.7884</v>
+      </c>
+      <c r="M52" s="4" t="n">
+        <v>0.5065</v>
+      </c>
+      <c r="N52" s="4" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="O52" s="4" t="n">
+        <v>0.5137</v>
+      </c>
+      <c r="P52" s="4" t="n">
+        <v>0.8744</v>
+      </c>
+      <c r="Q52" s="4" t="n">
+        <v>0.9004</v>
+      </c>
+      <c r="R52" s="4" t="n">
+        <v>0.8909</v>
+      </c>
+      <c r="S52" s="4" t="n">
+        <v>0.5985</v>
+      </c>
+      <c r="T52" s="4" t="n">
+        <v>0.7746</v>
+      </c>
+      <c r="U52" s="4" t="n">
+        <v>0.9284</v>
+      </c>
+      <c r="V52" s="4" t="n">
+        <v>0.5543</v>
+      </c>
+      <c r="W52" s="4" t="n">
+        <v>0.4074</v>
+      </c>
+      <c r="X52" s="4" t="n">
+        <v>0.6864</v>
+      </c>
+      <c r="Y52" s="4" t="n">
+        <v>0.5417</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>0.00847</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>0.9913</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>1.3145</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0.4557</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>0.7161999999999999</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.8166</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>0.8918</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>0.7868000000000001</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>0.7875</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>0.7872</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>0.7894</v>
+      </c>
+      <c r="M53" s="5" t="n">
+        <v>0.5061</v>
+      </c>
+      <c r="N53" s="5" t="n">
+        <v>0.9192</v>
+      </c>
+      <c r="O53" s="5" t="n">
+        <v>0.5131</v>
+      </c>
+      <c r="P53" s="5" t="n">
+        <v>0.8796</v>
+      </c>
+      <c r="Q53" s="5" t="n">
+        <v>0.8968</v>
+      </c>
+      <c r="R53" s="5" t="n">
+        <v>0.8897</v>
+      </c>
+      <c r="S53" s="5" t="n">
+        <v>0.5961</v>
+      </c>
+      <c r="T53" s="5" t="n">
+        <v>0.7758</v>
+      </c>
+      <c r="U53" s="5" t="n">
+        <v>0.9242</v>
+      </c>
+      <c r="V53" s="5" t="n">
+        <v>0.5591</v>
+      </c>
+      <c r="W53" s="5" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="X53" s="5" t="n">
+        <v>0.7050999999999999</v>
+      </c>
+      <c r="Y53" s="5" t="n">
+        <v>0.5417</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>0.00844</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>1.2161</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>1.3151</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>0.6856</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>0.7161</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>0.8549</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>0.8919</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>0.7991</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>0.7826</v>
+      </c>
+      <c r="K54" s="4" t="n">
+        <v>0.7907</v>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>0.7927</v>
+      </c>
+      <c r="M54" s="4" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="N54" s="4" t="n">
+        <v>0.9191</v>
+      </c>
+      <c r="O54" s="4" t="n">
+        <v>0.5135999999999999</v>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>0.8937</v>
+      </c>
+      <c r="Q54" s="4" t="n">
+        <v>0.8882</v>
+      </c>
+      <c r="R54" s="4" t="n">
+        <v>0.8898</v>
+      </c>
+      <c r="S54" s="4" t="n">
+        <v>0.5972</v>
+      </c>
+      <c r="T54" s="4" t="n">
+        <v>0.7865</v>
+      </c>
+      <c r="U54" s="4" t="n">
+        <v>0.9179</v>
+      </c>
+      <c r="V54" s="4" t="n">
+        <v>0.5691000000000001</v>
+      </c>
+      <c r="W54" s="4" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="X54" s="4" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="Y54" s="4" t="n">
+        <v>0.5417</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>0.00844</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>1.2161</v>
+      </c>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n">
+        <v>0.6856</v>
+      </c>
+      <c r="F55" s="5" t="n"/>
+      <c r="G55" s="5" t="n">
+        <v>0.8549</v>
+      </c>
+      <c r="H55" s="5" t="n"/>
+      <c r="I55" s="5" t="n">
+        <v>0.7678</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>0.7763</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="M55" s="5" t="n">
+        <v>0.5141</v>
+      </c>
+      <c r="N55" s="5" t="n">
+        <v>0.9161</v>
+      </c>
+      <c r="O55" s="5" t="n">
+        <v>0.5111</v>
+      </c>
+      <c r="P55" s="5" t="n">
+        <v>0.8625</v>
+      </c>
+      <c r="Q55" s="5" t="n">
+        <v>0.9046999999999999</v>
+      </c>
+      <c r="R55" s="5" t="n">
+        <v>0.8912</v>
+      </c>
+      <c r="S55" s="5" t="n">
+        <v>0.6009</v>
+      </c>
+      <c r="T55" s="5" t="n">
+        <v>0.7668</v>
+      </c>
+      <c r="U55" s="5" t="n">
+        <v>0.9329</v>
+      </c>
+      <c r="V55" s="5" t="n">
+        <v>0.5655</v>
+      </c>
+      <c r="W55" s="5" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="X55" s="5" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="Y55" s="5" t="n">
+        <v>0.5174</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
